--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ141"/>
+  <dimension ref="A1:AZ142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15475,64 +15475,56 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>136902331</v>
+        <v>136905789</v>
       </c>
       <c r="B123" t="n">
-        <v>58169</v>
+        <v>57857</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103021</v>
+        <v>102975</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kolmilberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>656216</v>
+        <v>656189</v>
       </c>
       <c r="R123" t="n">
-        <v>7024536</v>
+        <v>7024590</v>
       </c>
       <c r="S123" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15561,7 +15553,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15571,7 +15563,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Fjäder.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15586,70 +15583,78 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136902331</t>
+          <t>https://artportalen.se/Sighting/136905789</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>136902330</v>
+        <v>136902331</v>
       </c>
       <c r="B124" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kolmilberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>656256</v>
+        <v>656216</v>
       </c>
       <c r="R124" t="n">
-        <v>7024524</v>
+        <v>7024536</v>
       </c>
       <c r="S124" t="n">
         <v>3</v>
@@ -15681,7 +15686,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15691,7 +15696,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15717,13 +15722,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136902330</t>
+          <t>https://artportalen.se/Sighting/136902331</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>136902391</v>
+        <v>136902330</v>
       </c>
       <c r="B125" t="n">
         <v>58164</v>
@@ -15751,36 +15756,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kolmilberget, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>656300</v>
+        <v>656256</v>
       </c>
       <c r="R125" t="n">
-        <v>7024715</v>
+        <v>7024524</v>
       </c>
       <c r="S125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -15809,7 +15806,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15819,7 +15816,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15845,13 +15842,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136902391</t>
+          <t>https://artportalen.se/Sighting/136902330</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>136908174</v>
+        <v>136902391</v>
       </c>
       <c r="B126" t="n">
         <v>58164</v>
@@ -15881,7 +15878,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -15902,13 +15899,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>656169</v>
+        <v>656300</v>
       </c>
       <c r="R126" t="n">
-        <v>7024720</v>
+        <v>7024715</v>
       </c>
       <c r="S126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15937,7 +15934,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15947,7 +15944,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15973,33 +15970,33 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136908174</t>
+          <t>https://artportalen.se/Sighting/136902391</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>136902344</v>
+        <v>136908174</v>
       </c>
       <c r="B127" t="n">
-        <v>56739</v>
+        <v>58164</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>206046</v>
+        <v>103023</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -16007,25 +16004,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Kolmilberget, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>656235</v>
+        <v>656169</v>
       </c>
       <c r="R127" t="n">
-        <v>7024590</v>
+        <v>7024720</v>
       </c>
       <c r="S127" t="n">
         <v>3</v>
@@ -16057,7 +16062,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -16067,7 +16072,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -16087,19 +16092,19 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136902344</t>
+          <t>https://artportalen.se/Sighting/136908174</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>136905761</v>
+        <v>136902344</v>
       </c>
       <c r="B128" t="n">
         <v>56739</v>
@@ -16127,16 +16132,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -16146,13 +16147,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>656246</v>
+        <v>656235</v>
       </c>
       <c r="R128" t="n">
-        <v>7024645</v>
+        <v>7024590</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -16181,7 +16182,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -16191,7 +16192,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16206,55 +16207,63 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Monika Norberg</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136905761</t>
+          <t>https://artportalen.se/Sighting/136902344</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>136908170</v>
+        <v>136905761</v>
       </c>
       <c r="B129" t="n">
-        <v>99270</v>
+        <v>56739</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219790</v>
+        <v>206046</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -16262,13 +16271,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>656283</v>
+        <v>656246</v>
       </c>
       <c r="R129" t="n">
-        <v>7024663</v>
+        <v>7024645</v>
       </c>
       <c r="S129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -16297,7 +16306,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -16307,7 +16316,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16316,31 +16325,30 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg</t>
+          <t>Ann-Christine Borja, Markus Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136908170</t>
+          <t>https://artportalen.se/Sighting/136905761</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>136908171</v>
+        <v>136908170</v>
       </c>
       <c r="B130" t="n">
         <v>99270</v>
@@ -16379,13 +16387,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>656258</v>
+        <v>656283</v>
       </c>
       <c r="R130" t="n">
-        <v>7024675</v>
+        <v>7024663</v>
       </c>
       <c r="S130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -16414,7 +16422,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -16424,7 +16432,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16451,50 +16459,42 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136908171</t>
+          <t>https://artportalen.se/Sighting/136908170</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>136902349</v>
+        <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99353</v>
+        <v>99270</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>1160</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
@@ -16504,13 +16504,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>656228</v>
+        <v>656258</v>
       </c>
       <c r="R131" t="n">
-        <v>7024646</v>
+        <v>7024675</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16558,6 +16558,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -16569,60 +16570,72 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja</t>
+          <t>Markus Borja, Monika Norberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136902349</t>
+          <t>https://artportalen.se/Sighting/136908171</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>136902347</v>
+        <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>98215</v>
+        <v>99353</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kolmilberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>656206</v>
+        <v>656228</v>
       </c>
       <c r="R132" t="n">
-        <v>7024666</v>
+        <v>7024646</v>
       </c>
       <c r="S132" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16651,7 +16664,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -16661,7 +16674,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16687,13 +16700,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136902347</t>
+          <t>https://artportalen.se/Sighting/136902349</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>136902362</v>
+        <v>136902347</v>
       </c>
       <c r="B133" t="n">
         <v>98215</v>
@@ -16728,10 +16741,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>656257</v>
+        <v>656206</v>
       </c>
       <c r="R133" t="n">
-        <v>7024689</v>
+        <v>7024666</v>
       </c>
       <c r="S133" t="n">
         <v>4</v>
@@ -16763,7 +16776,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16773,7 +16786,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16799,13 +16812,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136902362</t>
+          <t>https://artportalen.se/Sighting/136902347</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>136902395</v>
+        <v>136902362</v>
       </c>
       <c r="B134" t="n">
         <v>98215</v>
@@ -16840,13 +16853,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>656284</v>
+        <v>656257</v>
       </c>
       <c r="R134" t="n">
-        <v>7024696</v>
+        <v>7024689</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16875,7 +16888,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16885,7 +16898,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16911,13 +16924,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136902395</t>
+          <t>https://artportalen.se/Sighting/136902362</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>136905787</v>
+        <v>136902395</v>
       </c>
       <c r="B135" t="n">
         <v>98215</v>
@@ -16952,13 +16965,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>656267</v>
+        <v>656284</v>
       </c>
       <c r="R135" t="n">
-        <v>7024623</v>
+        <v>7024696</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16987,7 +17000,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16997,7 +17010,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17012,24 +17025,24 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136905787</t>
+          <t>https://artportalen.se/Sighting/136902395</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>136908168</v>
+        <v>136905787</v>
       </c>
       <c r="B136" t="n">
         <v>98215</v>
@@ -17064,13 +17077,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>656215</v>
+        <v>656267</v>
       </c>
       <c r="R136" t="n">
-        <v>7024656</v>
+        <v>7024623</v>
       </c>
       <c r="S136" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -17099,7 +17112,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -17109,7 +17122,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17124,27 +17137,27 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136908168</t>
+          <t>https://artportalen.se/Sighting/136905787</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>136902335</v>
+        <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>80541</v>
+        <v>98215</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17152,40 +17165,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kolmilberget, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>656280</v>
+        <v>656215</v>
       </c>
       <c r="R137" t="n">
-        <v>7024541</v>
+        <v>7024656</v>
       </c>
       <c r="S137" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -17214,7 +17224,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -17224,7 +17234,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17235,21 +17245,6 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
@@ -17265,13 +17260,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136902335</t>
+          <t>https://artportalen.se/Sighting/136908168</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>136902378</v>
+        <v>136902335</v>
       </c>
       <c r="B138" t="n">
         <v>80541</v>
@@ -17300,16 +17295,19 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Kolmilberget, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>656144</v>
+        <v>656280</v>
       </c>
       <c r="R138" t="n">
-        <v>7024789</v>
+        <v>7024541</v>
       </c>
       <c r="S138" t="n">
         <v>3</v>
@@ -17341,7 +17339,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -17351,7 +17349,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -17362,6 +17360,21 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -17377,13 +17390,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136902378</t>
+          <t>https://artportalen.se/Sighting/136902335</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>136905777</v>
+        <v>136902378</v>
       </c>
       <c r="B139" t="n">
         <v>80541</v>
@@ -17412,22 +17425,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Kolmilberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>656128</v>
+        <v>656144</v>
       </c>
       <c r="R139" t="n">
-        <v>7024804</v>
+        <v>7024789</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -17456,7 +17466,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17466,7 +17476,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17475,87 +17485,74 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136905777</t>
+          <t>https://artportalen.se/Sighting/136902378</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>136902393</v>
+        <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>79499</v>
+        <v>80541</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>260591</v>
+        <v>229497</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kolmilberget, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>656310</v>
+        <v>656128</v>
       </c>
       <c r="R140" t="n">
-        <v>7024708</v>
+        <v>7024804</v>
       </c>
       <c r="S140" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -17584,7 +17581,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17594,7 +17591,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17603,33 +17600,49 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Markus Borja, Monika Norberg, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136902393</t>
+          <t>https://artportalen.se/Sighting/136905777</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>136908160</v>
+        <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>92505</v>
+        <v>79499</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17637,40 +17650,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6040186</v>
+        <v>260591</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Kolmilberget, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>656286</v>
+        <v>656310</v>
       </c>
       <c r="R141" t="n">
-        <v>7024577</v>
+        <v>7024708</v>
       </c>
       <c r="S141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -17699,7 +17709,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17709,7 +17719,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17718,7 +17728,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -17735,6 +17744,122 @@
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136902393</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>136908160</v>
+      </c>
+      <c r="B142" t="n">
+        <v>92505</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Kolmilberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>656286</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7024577</v>
+      </c>
+      <c r="S142" t="n">
+        <v>3</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Sidensjö</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Markus Borja, Monika Norberg, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136908160</t>
         </is>
@@ -17882,6 +18007,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80541</v>
+        <v>80545</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80541</v>
+        <v>80545</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80541</v>
+        <v>80545</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92505</v>
+        <v>92507</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92126</v>
+        <v>92128</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80545</v>
+        <v>80547</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80545</v>
+        <v>80547</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80545</v>
+        <v>80547</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92507</v>
+        <v>92509</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92128</v>
+        <v>92129</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80547</v>
+        <v>80548</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80547</v>
+        <v>80548</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80547</v>
+        <v>80548</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92129</v>
+        <v>92135</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92510</v>
+        <v>92516</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80548</v>
+        <v>80550</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80548</v>
+        <v>80550</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80548</v>
+        <v>80550</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92516</v>
+        <v>92520</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -16351,7 +16351,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80550</v>
+        <v>80553</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80550</v>
+        <v>80553</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80550</v>
+        <v>80553</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>136902386</v>
       </c>
       <c r="B106" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>136902334</v>
       </c>
       <c r="B107" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>136902338</v>
       </c>
       <c r="B108" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>136902364</v>
       </c>
       <c r="B109" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>136902367</v>
       </c>
       <c r="B110" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>136902373</v>
       </c>
       <c r="B111" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>136902375</v>
       </c>
       <c r="B112" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>136902389</v>
       </c>
       <c r="B113" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>136902396</v>
       </c>
       <c r="B114" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>136902399</v>
       </c>
       <c r="B115" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>136902400</v>
       </c>
       <c r="B116" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>136902402</v>
       </c>
       <c r="B117" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>136905776</v>
       </c>
       <c r="B118" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>136905779</v>
       </c>
       <c r="B119" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>136905785</v>
       </c>
       <c r="B120" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>136908182</v>
       </c>
       <c r="B121" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>136908185</v>
       </c>
       <c r="B122" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>136905789</v>
       </c>
       <c r="B123" t="n">
-        <v>57857</v>
+        <v>57870</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>136902331</v>
       </c>
       <c r="B124" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>136902330</v>
       </c>
       <c r="B125" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>136902391</v>
       </c>
       <c r="B126" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>136908174</v>
       </c>
       <c r="B127" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>136902344</v>
       </c>
       <c r="B128" t="n">
-        <v>56739</v>
+        <v>56752</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>136905761</v>
       </c>
       <c r="B129" t="n">
-        <v>56739</v>
+        <v>56752</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80553</v>
+        <v>80566</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80553</v>
+        <v>80566</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80553</v>
+        <v>80566</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92522</v>
+        <v>92535</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92154</v>
+        <v>92156</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>136902386</v>
       </c>
       <c r="B106" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>136902334</v>
       </c>
       <c r="B107" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>136902338</v>
       </c>
       <c r="B108" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>136902364</v>
       </c>
       <c r="B109" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>136902367</v>
       </c>
       <c r="B110" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>136902373</v>
       </c>
       <c r="B111" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>136902375</v>
       </c>
       <c r="B112" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>136902389</v>
       </c>
       <c r="B113" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>136902396</v>
       </c>
       <c r="B114" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>136902399</v>
       </c>
       <c r="B115" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>136902400</v>
       </c>
       <c r="B116" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>136902402</v>
       </c>
       <c r="B117" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>136905776</v>
       </c>
       <c r="B118" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>136905779</v>
       </c>
       <c r="B119" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>136905785</v>
       </c>
       <c r="B120" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>136908182</v>
       </c>
       <c r="B121" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>136908185</v>
       </c>
       <c r="B122" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>136905789</v>
       </c>
       <c r="B123" t="n">
-        <v>57870</v>
+        <v>57872</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>136902331</v>
       </c>
       <c r="B124" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>136902330</v>
       </c>
       <c r="B125" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>136902391</v>
       </c>
       <c r="B126" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>136908174</v>
       </c>
       <c r="B127" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>136902344</v>
       </c>
       <c r="B128" t="n">
-        <v>56752</v>
+        <v>56754</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>136905761</v>
       </c>
       <c r="B129" t="n">
-        <v>56752</v>
+        <v>56754</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80566</v>
+        <v>80568</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80566</v>
+        <v>80568</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80566</v>
+        <v>80568</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92535</v>
+        <v>92537</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -7100,11 +7100,7 @@
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -11582,11 +11578,7 @@
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -13398,11 +13390,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -13518,11 +13506,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -13643,11 +13627,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -13768,11 +13748,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -13893,11 +13869,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -14018,11 +13990,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -14143,11 +14111,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -14268,11 +14232,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -14393,11 +14353,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -14518,11 +14474,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -14643,11 +14595,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -14768,11 +14716,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -14893,11 +14837,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -15018,11 +14958,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -15143,11 +15079,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -15506,11 +15438,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -15635,11 +15563,7 @@
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -15759,11 +15683,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -15883,11 +15803,7 @@
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -16011,11 +15927,7 @@
       </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -16135,11 +16047,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -16259,11 +16167,7 @@
       </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92156</v>
+        <v>92159</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92537</v>
+        <v>92540</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92159</v>
+        <v>92169</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>136902386</v>
       </c>
       <c r="B106" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>136902334</v>
       </c>
       <c r="B107" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>136902338</v>
       </c>
       <c r="B108" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136902364</v>
       </c>
       <c r="B109" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>136902367</v>
       </c>
       <c r="B110" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>136902373</v>
       </c>
       <c r="B111" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>136902375</v>
       </c>
       <c r="B112" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>136902389</v>
       </c>
       <c r="B113" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>136902396</v>
       </c>
       <c r="B114" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>136902399</v>
       </c>
       <c r="B115" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>136902400</v>
       </c>
       <c r="B116" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>136902402</v>
       </c>
       <c r="B117" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>136905776</v>
       </c>
       <c r="B118" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>136905779</v>
       </c>
       <c r="B119" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>136905785</v>
       </c>
       <c r="B120" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>136908182</v>
       </c>
       <c r="B121" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>136908185</v>
       </c>
       <c r="B122" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>136905789</v>
       </c>
       <c r="B123" t="n">
-        <v>57872</v>
+        <v>57882</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>136902331</v>
       </c>
       <c r="B124" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>136902330</v>
       </c>
       <c r="B125" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>136902391</v>
       </c>
       <c r="B126" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>136908174</v>
       </c>
       <c r="B127" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>136902344</v>
       </c>
       <c r="B128" t="n">
-        <v>56754</v>
+        <v>56764</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>136905761</v>
       </c>
       <c r="B129" t="n">
-        <v>56754</v>
+        <v>56764</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80568</v>
+        <v>80578</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80568</v>
+        <v>80578</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80568</v>
+        <v>80578</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92540</v>
+        <v>92550</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92169</v>
+        <v>92170</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92550</v>
+        <v>92551</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92170</v>
+        <v>92173</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>136902386</v>
       </c>
       <c r="B106" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>136902334</v>
       </c>
       <c r="B107" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>136902338</v>
       </c>
       <c r="B108" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136902364</v>
       </c>
       <c r="B109" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>136902367</v>
       </c>
       <c r="B110" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>136902373</v>
       </c>
       <c r="B111" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>136902375</v>
       </c>
       <c r="B112" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>136902389</v>
       </c>
       <c r="B113" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>136902396</v>
       </c>
       <c r="B114" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>136902399</v>
       </c>
       <c r="B115" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>136902400</v>
       </c>
       <c r="B116" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>136902402</v>
       </c>
       <c r="B117" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>136905776</v>
       </c>
       <c r="B118" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>136905779</v>
       </c>
       <c r="B119" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>136905785</v>
       </c>
       <c r="B120" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>136908182</v>
       </c>
       <c r="B121" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>136908185</v>
       </c>
       <c r="B122" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>136905789</v>
       </c>
       <c r="B123" t="n">
-        <v>57882</v>
+        <v>57883</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>136902331</v>
       </c>
       <c r="B124" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>136902330</v>
       </c>
       <c r="B125" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>136902391</v>
       </c>
       <c r="B126" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>136908174</v>
       </c>
       <c r="B127" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>136902344</v>
       </c>
       <c r="B128" t="n">
-        <v>56764</v>
+        <v>56765</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>136905761</v>
       </c>
       <c r="B129" t="n">
-        <v>56764</v>
+        <v>56765</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92551</v>
+        <v>92554</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92173</v>
+        <v>92175</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92175</v>
+        <v>92180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>136902386</v>
       </c>
       <c r="B106" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>136902334</v>
       </c>
       <c r="B107" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>136902338</v>
       </c>
       <c r="B108" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136902364</v>
       </c>
       <c r="B109" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>136902367</v>
       </c>
       <c r="B110" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>136902373</v>
       </c>
       <c r="B111" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>136902375</v>
       </c>
       <c r="B112" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>136902389</v>
       </c>
       <c r="B113" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>136902396</v>
       </c>
       <c r="B114" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>136902399</v>
       </c>
       <c r="B115" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>136902400</v>
       </c>
       <c r="B116" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>136902402</v>
       </c>
       <c r="B117" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>136905776</v>
       </c>
       <c r="B118" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>136905779</v>
       </c>
       <c r="B119" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>136905785</v>
       </c>
       <c r="B120" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>136908182</v>
       </c>
       <c r="B121" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>136908185</v>
       </c>
       <c r="B122" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>136905789</v>
       </c>
       <c r="B123" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>136902331</v>
       </c>
       <c r="B124" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>136902330</v>
       </c>
       <c r="B125" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>136902391</v>
       </c>
       <c r="B126" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>136908174</v>
       </c>
       <c r="B127" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92556</v>
+        <v>92561</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92180</v>
+        <v>92192</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92561</v>
+        <v>92573</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92573</v>
+        <v>92574</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 10278-2026 artfynd.xlsx
+++ b/artfynd/A 10278-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136902368</v>
       </c>
       <c r="B2" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136902354</v>
       </c>
       <c r="B3" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136902370</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136902398</v>
       </c>
       <c r="B5" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136905744</v>
       </c>
       <c r="B6" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136905747</v>
       </c>
       <c r="B7" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136908184</v>
       </c>
       <c r="B8" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136902341</v>
       </c>
       <c r="B9" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>136902345</v>
       </c>
       <c r="B10" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>136902350</v>
       </c>
       <c r="B11" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>136902356</v>
       </c>
       <c r="B12" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>136902377</v>
       </c>
       <c r="B13" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>136905757</v>
       </c>
       <c r="B14" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136905773</v>
       </c>
       <c r="B15" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>136908161</v>
       </c>
       <c r="B16" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136908162</v>
       </c>
       <c r="B17" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136908163</v>
       </c>
       <c r="B18" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>136908167</v>
       </c>
       <c r="B19" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>136908175</v>
       </c>
       <c r="B20" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>136908177</v>
       </c>
       <c r="B21" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>136908179</v>
       </c>
       <c r="B22" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136908183</v>
       </c>
       <c r="B23" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136902346</v>
       </c>
       <c r="B24" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>136902358</v>
       </c>
       <c r="B25" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>136902366</v>
       </c>
       <c r="B26" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>136902376</v>
       </c>
       <c r="B27" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>136905767</v>
       </c>
       <c r="B28" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>136908173</v>
       </c>
       <c r="B29" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136905746</v>
       </c>
       <c r="B30" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>136902329</v>
       </c>
       <c r="B31" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>136902342</v>
       </c>
       <c r="B32" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136902361</v>
       </c>
       <c r="B33" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>136905764</v>
       </c>
       <c r="B34" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>136908176</v>
       </c>
       <c r="B35" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>136902340</v>
       </c>
       <c r="B36" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>136902348</v>
       </c>
       <c r="B37" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>136902351</v>
       </c>
       <c r="B38" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>136902357</v>
       </c>
       <c r="B39" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136902359</v>
       </c>
       <c r="B40" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>136902372</v>
       </c>
       <c r="B41" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>136905745</v>
       </c>
       <c r="B42" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136905748</v>
       </c>
       <c r="B43" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>136905749</v>
       </c>
       <c r="B44" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136905750</v>
       </c>
       <c r="B45" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>136905752</v>
       </c>
       <c r="B46" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>136905755</v>
       </c>
       <c r="B47" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>136905758</v>
       </c>
       <c r="B48" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>136905762</v>
       </c>
       <c r="B49" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>136905763</v>
       </c>
       <c r="B50" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>136905765</v>
       </c>
       <c r="B51" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>136905780</v>
       </c>
       <c r="B52" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>136908158</v>
       </c>
       <c r="B53" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>136902325</v>
       </c>
       <c r="B54" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>136902326</v>
       </c>
       <c r="B55" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>136902327</v>
       </c>
       <c r="B56" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>136902336</v>
       </c>
       <c r="B57" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>136902355</v>
       </c>
       <c r="B58" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>136902374</v>
       </c>
       <c r="B59" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>136902388</v>
       </c>
       <c r="B60" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>136902390</v>
       </c>
       <c r="B61" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>136902392</v>
       </c>
       <c r="B62" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>136902394</v>
       </c>
       <c r="B63" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>136905740</v>
       </c>
       <c r="B64" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>136905741</v>
       </c>
       <c r="B65" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>136905742</v>
       </c>
       <c r="B66" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>136905743</v>
       </c>
       <c r="B67" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>136905753</v>
       </c>
       <c r="B68" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>136905754</v>
       </c>
       <c r="B69" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>136905768</v>
       </c>
       <c r="B70" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>136905769</v>
       </c>
       <c r="B71" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136905770</v>
       </c>
       <c r="B72" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>136905771</v>
       </c>
       <c r="B73" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>136905772</v>
       </c>
       <c r="B74" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>136905774</v>
       </c>
       <c r="B75" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136905775</v>
       </c>
       <c r="B76" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>136905782</v>
       </c>
       <c r="B77" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>136905783</v>
       </c>
       <c r="B78" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>136905784</v>
       </c>
       <c r="B79" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>136905786</v>
       </c>
       <c r="B80" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>136908169</v>
       </c>
       <c r="B81" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>136902328</v>
       </c>
       <c r="B82" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136905781</v>
       </c>
       <c r="B83" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>136908159</v>
       </c>
       <c r="B84" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>136902332</v>
       </c>
       <c r="B85" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>136902352</v>
       </c>
       <c r="B86" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>136902379</v>
       </c>
       <c r="B87" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>136902383</v>
       </c>
       <c r="B88" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>136902384</v>
       </c>
       <c r="B89" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>136902387</v>
       </c>
       <c r="B90" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>136905756</v>
       </c>
       <c r="B91" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>136908166</v>
       </c>
       <c r="B92" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>136908172</v>
       </c>
       <c r="B93" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>136908178</v>
       </c>
       <c r="B94" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>136908180</v>
       </c>
       <c r="B95" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>136902353</v>
       </c>
       <c r="B96" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136902363</v>
       </c>
       <c r="B97" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>136902381</v>
       </c>
       <c r="B98" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>136905778</v>
       </c>
       <c r="B99" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>136902333</v>
       </c>
       <c r="B100" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>136902360</v>
       </c>
       <c r="B101" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>136902380</v>
       </c>
       <c r="B102" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>136905766</v>
       </c>
       <c r="B103" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>136908164</v>
       </c>
       <c r="B104" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>136908165</v>
       </c>
       <c r="B105" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>136908170</v>
       </c>
       <c r="B130" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>136908171</v>
       </c>
       <c r="B131" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>136902349</v>
       </c>
       <c r="B132" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>136902347</v>
       </c>
       <c r="B133" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>136902362</v>
       </c>
       <c r="B134" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>136902395</v>
       </c>
       <c r="B135" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>136905787</v>
       </c>
       <c r="B136" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>136908168</v>
       </c>
       <c r="B137" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>136902335</v>
       </c>
       <c r="B138" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>136902378</v>
       </c>
       <c r="B139" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>136905777</v>
       </c>
       <c r="B140" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>136902393</v>
       </c>
       <c r="B141" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>136908160</v>
       </c>
       <c r="B142" t="n">
-        <v>92574</v>
+        <v>92577</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
